--- a/target/test-classes/testcase.xlsx
+++ b/target/test-classes/testcase.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="58">
   <si>
     <t xml:space="preserve">S.no</t>
   </si>
@@ -37,28 +37,28 @@
     <t xml:space="preserve">Domestic – OW</t>
   </si>
   <si>
-    <t xml:space="preserve">Order Id : 2152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6894</t>
+    <t xml:space="preserve">Order Id : 2300</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7021</t>
   </si>
   <si>
     <t xml:space="preserve">Domestic – RT</t>
   </si>
   <si>
-    <t xml:space="preserve">Order Id : 2223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6949</t>
+    <t xml:space="preserve">Order Id : 2302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7023</t>
   </si>
   <si>
     <t xml:space="preserve">International – OW</t>
   </si>
   <si>
-    <t xml:space="preserve">Order Id : 2225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6951</t>
+    <t xml:space="preserve">Order Id : 2304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7025</t>
   </si>
   <si>
     <t xml:space="preserve">International – RT</t>
@@ -73,19 +73,19 @@
     <t xml:space="preserve">Corporate User Domestic – OW </t>
   </si>
   <si>
-    <t xml:space="preserve">Order Id : 2154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6896</t>
+    <t xml:space="preserve">Order Id : 2301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7022</t>
   </si>
   <si>
     <t xml:space="preserve">Corporate User Domestic – RT</t>
   </si>
   <si>
-    <t xml:space="preserve">Order Id : 2156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6898</t>
+    <t xml:space="preserve">Order Id : 2303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7024</t>
   </si>
   <si>
     <t xml:space="preserve">Corporate User International – OW</t>
@@ -100,10 +100,10 @@
     <t xml:space="preserve">Corporate User International – RT</t>
   </si>
   <si>
-    <t xml:space="preserve">Order Id : 2230</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6956</t>
+    <t xml:space="preserve">Order Id : 2330</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7050</t>
   </si>
   <si>
     <t xml:space="preserve">Hotel booking details</t>
@@ -133,31 +133,67 @@
     <t xml:space="preserve">Car booking by – CA user</t>
   </si>
   <si>
-    <t xml:space="preserve">Order Id : 2266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6988</t>
+    <t xml:space="preserve">Order Id : 2298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7019</t>
   </si>
   <si>
     <t xml:space="preserve">Car booking by – CU user</t>
   </si>
   <si>
-    <t xml:space="preserve">Order Id : 2259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6981</t>
+    <t xml:space="preserve">Order Id : 2299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Visa booking details</t>
   </si>
   <si>
     <t xml:space="preserve">Visa booking by – CA user</t>
   </si>
   <si>
+    <t xml:space="preserve">Order Id : 2282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7004</t>
+  </si>
+  <si>
     <t xml:space="preserve">Visa booking by – CU user</t>
   </si>
   <si>
-    <t>Order Id : 2282</t>
-  </si>
-  <si>
-    <t>7004</t>
+    <t xml:space="preserve">Order Id : 2292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Insurance booking details</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Order Id : 2342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Order Id : 2348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Combination booking details</t>
+  </si>
+  <si>
+    <t>7088</t>
+  </si>
+  <si>
+    <t>7098</t>
+  </si>
+  <si>
+    <t>7099</t>
   </si>
 </sst>
 </file>
@@ -351,8 +387,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
-  <sheetFormatPr defaultColWidth="12.00390625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:D24"/>
+  <sheetFormatPr defaultColWidth="12.07421875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="2" max="2" customWidth="true" hidden="false" style="0" width="37.23" collapsed="true" outlineLevel="0"/>
     <col min="3" max="3" customWidth="true" hidden="false" style="0" width="13.36" collapsed="true" outlineLevel="0"/>
@@ -559,7 +595,7 @@
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
@@ -570,7 +606,7 @@
         <v>13</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>44</v>
@@ -584,16 +620,88 @@
         <v>14</v>
       </c>
       <c r="B18" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B19" s="3"/>
+      <c r="C19" s="3"/>
+      <c r="D19" s="3"/>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B20" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
+      <c r="C20" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B22" s="3"/>
+      <c r="C22" s="3"/>
+      <c r="D22" s="3"/>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="5">
     <mergeCell ref="A10:D10"/>
     <mergeCell ref="A13:D13"/>
     <mergeCell ref="A16:D16"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="A22:D22"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>

--- a/target/test-classes/testcase.xlsx
+++ b/target/test-classes/testcase.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="100">
   <si>
     <t xml:space="preserve">S.no</t>
   </si>
@@ -55,28 +55,28 @@
     <t xml:space="preserve">Domestic – OW</t>
   </si>
   <si>
-    <t xml:space="preserve">3389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1905.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55624.5</t>
+    <t xml:space="preserve">3494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1999.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19917.5</t>
   </si>
   <si>
     <t xml:space="preserve">Domestic – RT</t>
   </si>
   <si>
-    <t xml:space="preserve">2670</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7286</t>
+    <t xml:space="preserve">3485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7897</t>
   </si>
   <si>
     <t xml:space="preserve">-</t>
@@ -91,6 +91,15 @@
     <t xml:space="preserve">7025</t>
   </si>
   <si>
+    <t xml:space="preserve">46380</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12604.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">530860.5</t>
+  </si>
+  <si>
     <t xml:space="preserve">International – RT</t>
   </si>
   <si>
@@ -109,9 +118,6 @@
     <t xml:space="preserve">7825</t>
   </si>
   <si>
-    <t xml:space="preserve">1984</t>
-  </si>
-  <si>
     <t xml:space="preserve">2099.5</t>
   </si>
   <si>
@@ -172,10 +178,10 @@
     <t xml:space="preserve">Car booking by – CA user</t>
   </si>
   <si>
-    <t xml:space="preserve">2718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7328</t>
+    <t xml:space="preserve">3440</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7860</t>
   </si>
   <si>
     <t xml:space="preserve">Car booking by – CU user</t>
@@ -202,10 +208,10 @@
     <t xml:space="preserve">Visa booking by – CU user</t>
   </si>
   <si>
-    <t xml:space="preserve">3324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7774</t>
+    <t xml:space="preserve">3456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7875</t>
   </si>
   <si>
     <t xml:space="preserve">Insurance booking details</t>
@@ -217,10 +223,10 @@
     <t xml:space="preserve">7332</t>
   </si>
   <si>
-    <t xml:space="preserve">2725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7335</t>
+    <t xml:space="preserve">3458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7877</t>
   </si>
   <si>
     <t xml:space="preserve">Combination booking details</t>
@@ -259,43 +265,61 @@
     <t xml:space="preserve">Pending</t>
   </si>
   <si>
-    <t>1984</t>
-  </si>
-  <si>
-    <t>1999.5</t>
-  </si>
-  <si>
-    <t>7967</t>
-  </si>
-  <si>
-    <t>7967.0</t>
-  </si>
-  <si>
-    <t>46380</t>
-  </si>
-  <si>
-    <t>12604.5</t>
-  </si>
-  <si>
-    <t>530860.5</t>
-  </si>
-  <si>
-    <t>3433</t>
-  </si>
-  <si>
-    <t>7853</t>
-  </si>
-  <si>
-    <t>3437</t>
-  </si>
-  <si>
-    <t>7857</t>
-  </si>
-  <si>
-    <t>3440</t>
-  </si>
-  <si>
-    <t>7860</t>
+    <t xml:space="preserve">Flight Cancellation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Domestic OW -Flight cancellation – All passenger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Domestic OW -Flight cancellation – Partial passenger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3500</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Domestic RT -Flight cancellation –Segment Cancellation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Domestic RT -Flight cancellation –Cross pax cancellation</t>
+  </si>
+  <si>
+    <t>3507</t>
+  </si>
+  <si>
+    <t>7919</t>
+  </si>
+  <si>
+    <t>3519</t>
+  </si>
+  <si>
+    <t>7927</t>
+  </si>
+  <si>
+    <t>3522</t>
+  </si>
+  <si>
+    <t>7929</t>
+  </si>
+  <si>
+    <t>3616</t>
+  </si>
+  <si>
+    <t>7990</t>
   </si>
 </sst>
 </file>
@@ -521,8 +545,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J23"/>
-  <sheetFormatPr defaultColWidth="12.48828125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:J28"/>
+  <sheetFormatPr defaultColWidth="12.58984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="2" max="2" customWidth="true" hidden="false" style="0" width="37.23" collapsed="true" outlineLevel="0"/>
     <col min="3" max="3" customWidth="true" hidden="false" style="0" width="13.36" collapsed="true" outlineLevel="0"/>
@@ -579,22 +603,22 @@
         <v>12</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>79</v>
+        <v>13</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>80</v>
+        <v>14</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>81</v>
+        <v>15</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>81</v>
+        <v>15</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>82</v>
+        <v>15</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>81</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -643,22 +667,22 @@
         <v>22</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>83</v>
+        <v>23</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>84</v>
+        <v>24</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>85</v>
+        <v>25</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>85</v>
+        <v>25</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>85</v>
+        <v>25</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>85</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -666,13 +690,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>19</v>
@@ -698,31 +722,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -730,13 +754,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>19</v>
@@ -762,13 +786,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E8" s="5"/>
       <c r="F8" s="5"/>
@@ -782,13 +806,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E9" s="5" t="s">
         <v>19</v>
@@ -811,7 +835,7 @@
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B10" s="6"/>
       <c r="C10" s="6"/>
@@ -828,13 +852,13 @@
         <v>9</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E11" s="5"/>
       <c r="F11" s="5"/>
@@ -848,13 +872,13 @@
         <v>10</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E12" s="5"/>
       <c r="F12" s="5"/>
@@ -865,7 +889,7 @@
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B13" s="6"/>
       <c r="C13" s="6"/>
@@ -882,13 +906,13 @@
         <v>11</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="E14" s="5"/>
       <c r="F14" s="5"/>
@@ -902,13 +926,13 @@
         <v>12</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E15" s="5"/>
       <c r="F15" s="5"/>
@@ -919,7 +943,7 @@
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B16" s="6"/>
       <c r="C16" s="6"/>
@@ -936,13 +960,13 @@
         <v>13</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E17" s="5"/>
       <c r="F17" s="5"/>
@@ -956,13 +980,13 @@
         <v>14</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E18" s="5"/>
       <c r="F18" s="5"/>
@@ -973,7 +997,7 @@
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B19" s="6"/>
       <c r="C19" s="6"/>
@@ -990,13 +1014,13 @@
         <v>14</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E20" s="5"/>
       <c r="F20" s="5"/>
@@ -1010,13 +1034,13 @@
         <v>15</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E21" s="5"/>
       <c r="F21" s="5"/>
@@ -1027,26 +1051,26 @@
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="6" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B22" s="6"/>
       <c r="C22" s="6" t="s">
         <v>3</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1054,34 +1078,99 @@
         <v>16</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>78</v>
+        <v>80</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="B24" s="6"/>
+      <c r="C24" s="6"/>
+      <c r="D24" s="6"/>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="20.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="20.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="20.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>95</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
     <mergeCell ref="A10:D10"/>
     <mergeCell ref="A13:D13"/>
     <mergeCell ref="A16:D16"/>
     <mergeCell ref="A19:D19"/>
     <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A24:D24"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>

--- a/target/test-classes/testcase.xlsx
+++ b/target/test-classes/testcase.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="124">
   <si>
     <t xml:space="preserve">S.no</t>
   </si>
@@ -320,6 +320,78 @@
   </si>
   <si>
     <t>7990</t>
+  </si>
+  <si>
+    <t>3904</t>
+  </si>
+  <si>
+    <t>8211</t>
+  </si>
+  <si>
+    <t>1984</t>
+  </si>
+  <si>
+    <t>1999.5</t>
+  </si>
+  <si>
+    <t>19917.5</t>
+  </si>
+  <si>
+    <t>4482</t>
+  </si>
+  <si>
+    <t>8673</t>
+  </si>
+  <si>
+    <t>4488</t>
+  </si>
+  <si>
+    <t>8678</t>
+  </si>
+  <si>
+    <t>3983.5</t>
+  </si>
+  <si>
+    <t>4502</t>
+  </si>
+  <si>
+    <t>8690</t>
+  </si>
+  <si>
+    <t>4503</t>
+  </si>
+  <si>
+    <t>8691</t>
+  </si>
+  <si>
+    <t>4505</t>
+  </si>
+  <si>
+    <t>8693</t>
+  </si>
+  <si>
+    <t>4275</t>
+  </si>
+  <si>
+    <t>1905.5</t>
+  </si>
+  <si>
+    <t>30902.5</t>
+  </si>
+  <si>
+    <t>4530</t>
+  </si>
+  <si>
+    <t>8712</t>
+  </si>
+  <si>
+    <t>46380</t>
+  </si>
+  <si>
+    <t>12604.5</t>
+  </si>
+  <si>
+    <t>530860.5</t>
   </si>
 </sst>
 </file>
@@ -597,28 +669,28 @@
         <v>10</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>11</v>
+        <v>119</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>12</v>
+        <v>120</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>13</v>
+        <v>116</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>14</v>
+        <v>117</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>15</v>
+        <v>118</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>15</v>
+        <v>118</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>15</v>
+        <v>118</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>15</v>
+        <v>118</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -667,22 +739,22 @@
         <v>22</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>23</v>
+        <v>121</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>24</v>
+        <v>122</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>25</v>
+        <v>123</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>25</v>
+        <v>123</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>25</v>
+        <v>123</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>25</v>
+        <v>123</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -731,22 +803,22 @@
         <v>31</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>13</v>
+        <v>102</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>32</v>
+        <v>103</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>33</v>
+        <v>109</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>33</v>
+        <v>109</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>33</v>
+        <v>109</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>33</v>
+        <v>109</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -855,10 +927,10 @@
         <v>44</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>45</v>
+        <v>110</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>46</v>
+        <v>111</v>
       </c>
       <c r="E11" s="5"/>
       <c r="F11" s="5"/>
@@ -909,10 +981,10 @@
         <v>51</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>99</v>
+        <v>113</v>
       </c>
       <c r="E14" s="5"/>
       <c r="F14" s="5"/>
@@ -963,10 +1035,10 @@
         <v>58</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>59</v>
+        <v>114</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>60</v>
+        <v>115</v>
       </c>
       <c r="E17" s="5"/>
       <c r="F17" s="5"/>
@@ -983,10 +1055,10 @@
         <v>61</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>62</v>
+        <v>100</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>63</v>
+        <v>101</v>
       </c>
       <c r="E18" s="5"/>
       <c r="F18" s="5"/>
